--- a/docs/descargas/siniestros_inec_2019.xlsx
+++ b/docs/descargas/siniestros_inec_2019.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="Ra6ff18cf4df04d62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R46b28475496345af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2019" sheetId="3" r:id="R0fe23b1ebbc14b50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="4" r:id="Rf12b8d768cf24ac0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2022" sheetId="5" r:id="R088079640ef64876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2023" sheetId="6" r:id="R4806f39462b443e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="7" r:id="R8d46927361f84140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R482834abd7b24b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R4706920ff7394170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2019" sheetId="3" r:id="R91b9375a2e8b420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="4" r:id="Rfd1f5a5e850e476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2022" sheetId="5" r:id="R8a6e89f4401747bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2023" sheetId="6" r:id="R712554c5cabc4d61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="7" r:id="R0c5ae5424a0f467e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -550,7 +550,7 @@
         <x:v>Producto</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Descarga pública del Catálogo de datos del Observatorio REDSA</x:v>
+        <x:v>Descarga pública del Catálogo de datos del Observatorio de Seguridad Vial y Movilidad Sostenible</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
